--- a/test/test_data/test_excel.xlsx
+++ b/test/test_data/test_excel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oneunivers.sharepoint.com/sites/EnOSProductManagerSite/Shared Documents/2024-planning/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python-Learning\extract_doc\test\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{801BD533-D5BE-4A51-A825-5E10B2EFDE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C1A6BA3-F94A-4B44-99B6-B1D1AB34E6E5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFA37EE-F417-4323-8751-0385A3973EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="485" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="485" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Function Group" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="224">
   <si>
     <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -147,21 +147,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>数据核对1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据核对2</t>
-  </si>
-  <si>
-    <t>Foundation(Core) R&amp;D + Foundation(Core) PM = Core - Maintenance(总计)+Core - Roadmap(总计)+Core - Resource(总计)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DCM，Data，CBB同数据核对2逻辑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Category</t>
   </si>
   <si>
@@ -242,14 +227,6 @@
   </si>
   <si>
     <t>1. 表头对应的各个团队的成员，见【Team Members List】</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Core</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Data </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1491,12 +1468,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1504,6 +1475,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1515,21 +1495,6 @@
     <xf numFmtId="176" fontId="6" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="10" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1537,6 +1502,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="10" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1850,30 +1827,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18.600000000000001" customHeight="1">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="52" t="s">
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="52" t="s">
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="54"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="52"/>
     </row>
     <row r="2" spans="1:13" ht="19.149999999999999" customHeight="1">
-      <c r="A2" s="51"/>
+      <c r="A2" s="63"/>
       <c r="B2" s="16" t="s">
         <v>4</v>
       </c>
@@ -1921,10 +1898,10 @@
       <c r="C3" s="44">
         <v>2.2173913043478266</v>
       </c>
-      <c r="D3" s="58">
+      <c r="D3" s="53">
         <v>7.42</v>
       </c>
-      <c r="E3" s="55">
+      <c r="E3" s="56">
         <v>6</v>
       </c>
       <c r="F3" s="43">
@@ -1933,10 +1910,10 @@
       <c r="G3" s="44">
         <v>2.1880952380952383</v>
       </c>
-      <c r="H3" s="58">
+      <c r="H3" s="53">
         <v>6.94</v>
       </c>
-      <c r="I3" s="55">
+      <c r="I3" s="56">
         <v>6</v>
       </c>
       <c r="J3" s="43">
@@ -1945,10 +1922,10 @@
       <c r="K3" s="44">
         <v>2.0757575757575757</v>
       </c>
-      <c r="L3" s="58">
+      <c r="L3" s="53">
         <v>8.5500000000000007</v>
       </c>
-      <c r="M3" s="55">
+      <c r="M3" s="56">
         <v>6</v>
       </c>
     </row>
@@ -1962,24 +1939,24 @@
       <c r="C4" s="44">
         <v>3.7173913043478266</v>
       </c>
-      <c r="D4" s="59"/>
-      <c r="E4" s="56"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="57"/>
       <c r="F4" s="43">
         <v>10.516666666666664</v>
       </c>
       <c r="G4" s="44">
         <v>3.8023809523809522</v>
       </c>
-      <c r="H4" s="59"/>
-      <c r="I4" s="56"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="57"/>
       <c r="J4" s="43">
         <v>10.419191919191919</v>
       </c>
       <c r="K4" s="44">
         <v>3.5820707070707067</v>
       </c>
-      <c r="L4" s="59"/>
-      <c r="M4" s="56"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="57"/>
     </row>
     <row r="5" spans="1:13" ht="16.5">
       <c r="A5" s="42" t="s">
@@ -1991,24 +1968,24 @@
       <c r="C5" s="44">
         <v>2.7173913043478262</v>
       </c>
-      <c r="D5" s="59"/>
-      <c r="E5" s="56"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="57"/>
       <c r="F5" s="43">
         <v>9.6428571428571352</v>
       </c>
       <c r="G5" s="44">
         <v>2.5238095238095237</v>
       </c>
-      <c r="H5" s="59"/>
-      <c r="I5" s="56"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="57"/>
       <c r="J5" s="43">
         <v>10.194444444444443</v>
       </c>
       <c r="K5" s="44">
         <v>2.7638888888888888</v>
       </c>
-      <c r="L5" s="59"/>
-      <c r="M5" s="56"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="57"/>
     </row>
     <row r="6" spans="1:13" ht="16.5">
       <c r="A6" s="42" t="s">
@@ -2020,24 +1997,24 @@
       <c r="C6" s="44">
         <v>10.043478260869566</v>
       </c>
-      <c r="D6" s="59"/>
-      <c r="E6" s="56"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="57"/>
       <c r="F6" s="48">
         <v>33.190476190476097</v>
       </c>
       <c r="G6" s="44">
         <v>10.085714285714278</v>
       </c>
-      <c r="H6" s="59"/>
-      <c r="I6" s="56"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="57"/>
       <c r="J6" s="43">
         <v>31.482323232323235</v>
       </c>
       <c r="K6" s="44">
         <v>9.2708333333333304</v>
       </c>
-      <c r="L6" s="59"/>
-      <c r="M6" s="56"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="57"/>
     </row>
     <row r="7" spans="1:13" ht="16.5">
       <c r="A7" s="19" t="s">
@@ -2047,20 +2024,20 @@
         <v>7.0869565217391308</v>
       </c>
       <c r="C7" s="21"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="57"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="58"/>
       <c r="F7" s="20">
         <v>6.4285714285714279</v>
       </c>
       <c r="G7" s="21"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="57"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="58"/>
       <c r="J7" s="20">
         <v>3.9444444444444442</v>
       </c>
       <c r="K7" s="21"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="57"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="58"/>
     </row>
     <row r="8" spans="1:13" ht="17.25" thickBot="1">
       <c r="A8" s="38" t="s">
@@ -2086,7 +2063,7 @@
       <c r="M8" s="41"/>
     </row>
     <row r="9" spans="1:13" ht="16.5">
-      <c r="A9" s="61" t="s">
+      <c r="A9" s="64" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="22">
@@ -2139,28 +2116,28 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="17.25" thickBot="1">
-      <c r="A10" s="62"/>
-      <c r="B10" s="63">
+      <c r="A10" s="65"/>
+      <c r="B10" s="59">
         <f>SUM(B9:E9)</f>
         <v>105.80241106719357</v>
       </c>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="63">
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="59">
         <f>SUM(F9:I9)</f>
         <v>106.65190476190465</v>
       </c>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="65"/>
-      <c r="J10" s="63">
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="59">
         <f>SUM(J9:M9)</f>
         <v>104.03295454545454</v>
       </c>
-      <c r="K10" s="64"/>
-      <c r="L10" s="64"/>
-      <c r="M10" s="65"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="61"/>
     </row>
     <row r="13" spans="1:13" ht="16.5">
       <c r="A13" s="8" t="s">
@@ -2188,41 +2165,24 @@
       </c>
     </row>
     <row r="19" spans="1:12" ht="16.5">
-      <c r="C19" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="46">
-        <f>B10+'Maintenance VS Roadmap'!K13-D3-E3-B8-B7</f>
-        <v>138.01426877470348</v>
-      </c>
+      <c r="C19" s="45"/>
+      <c r="D19" s="46"/>
       <c r="E19" s="47"/>
       <c r="F19" s="47"/>
       <c r="G19" s="47"/>
-      <c r="H19" s="46">
-        <f>F10+'Maintenance VS Roadmap'!V13-H3-I3-F8-F7</f>
-        <v>133.38571428571419</v>
-      </c>
-      <c r="L19" s="46">
-        <f>J10+'Maintenance VS Roadmap'!AG13-L3-M3-J8-J7</f>
-        <v>132.4444444444444</v>
-      </c>
+      <c r="H19" s="46"/>
+      <c r="L19" s="46"/>
     </row>
     <row r="20" spans="1:12" ht="16.5">
-      <c r="C20" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="46" t="s">
-        <v>23</v>
-      </c>
+      <c r="C20" s="45"/>
+      <c r="D20" s="46"/>
       <c r="H20" s="25"/>
       <c r="I20" s="25"/>
       <c r="J20" s="25"/>
       <c r="K20" s="25"/>
     </row>
     <row r="21" spans="1:12" ht="16.5">
-      <c r="D21" s="46" t="s">
-        <v>24</v>
-      </c>
+      <c r="D21" s="46"/>
       <c r="H21" s="25"/>
       <c r="I21" s="25"/>
       <c r="J21" s="25"/>
@@ -2254,6 +2214,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="E3:E7"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B10:E10"/>
     <mergeCell ref="J1:M1"/>
     <mergeCell ref="L3:L7"/>
     <mergeCell ref="M3:M7"/>
@@ -2262,12 +2228,6 @@
     <mergeCell ref="H3:H7"/>
     <mergeCell ref="I3:I7"/>
     <mergeCell ref="F10:I10"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="E3:E7"/>
-    <mergeCell ref="D3:D7"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B10:E10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2304,10 +2264,10 @@
   <sheetData>
     <row r="1" spans="1:34" ht="17.25" thickBot="1">
       <c r="A1" s="66" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B1" s="66" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C1" s="68"/>
       <c r="D1" s="68"/>
@@ -2349,108 +2309,108 @@
     <row r="2" spans="1:34" ht="16.5">
       <c r="A2" s="67"/>
       <c r="B2" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="G2" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="H2" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="I2" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="J2" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="K2" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="L2" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="L2" s="35" t="s">
-        <v>37</v>
-      </c>
       <c r="M2" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="32" t="s">
+      <c r="R2" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="32" t="s">
+      <c r="S2" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="32" t="s">
+      <c r="T2" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" s="32" t="s">
+      <c r="U2" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="32" t="s">
+      <c r="V2" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="S2" s="32" t="s">
+      <c r="W2" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="T2" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="U2" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="V2" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="W2" s="35" t="s">
-        <v>37</v>
-      </c>
       <c r="X2" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y2" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z2" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA2" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB2" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="Y2" s="32" t="s">
+      <c r="AC2" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="32" t="s">
+      <c r="AD2" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="AA2" s="32" t="s">
+      <c r="AE2" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="AB2" s="32" t="s">
+      <c r="AF2" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="AC2" s="32" t="s">
+      <c r="AG2" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="AD2" s="32" t="s">
+      <c r="AH2" s="35" t="s">
         <v>33</v>
-      </c>
-      <c r="AE2" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF2" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG2" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH2" s="35" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:34" ht="16.5">
       <c r="A3" s="26" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3"/>
@@ -2519,7 +2479,7 @@
     </row>
     <row r="4" spans="1:34" ht="16.5">
       <c r="A4" s="26" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
@@ -2590,7 +2550,7 @@
     </row>
     <row r="5" spans="1:34" ht="16.5">
       <c r="A5" s="26" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>
@@ -2645,7 +2605,7 @@
     </row>
     <row r="6" spans="1:34" ht="16.5">
       <c r="A6" s="27" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B6" s="4">
         <v>0.40513833992094861</v>
@@ -2704,7 +2664,7 @@
     </row>
     <row r="7" spans="1:34" ht="16.5">
       <c r="A7" s="27" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B7" s="4">
         <v>8.8250988142292499</v>
@@ -2777,7 +2737,7 @@
     </row>
     <row r="8" spans="1:34" ht="16.5">
       <c r="A8" s="26" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="3"/>
@@ -2832,7 +2792,7 @@
     </row>
     <row r="9" spans="1:34" ht="16.5">
       <c r="A9" s="26" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="3">
@@ -2905,7 +2865,7 @@
     </row>
     <row r="10" spans="1:34" ht="16.5">
       <c r="A10" s="26" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="3"/>
@@ -2958,7 +2918,7 @@
     </row>
     <row r="11" spans="1:34" ht="16.5">
       <c r="A11" s="27" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
@@ -3035,7 +2995,7 @@
     </row>
     <row r="12" spans="1:34" ht="16.5">
       <c r="A12" s="27" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="5">
@@ -3124,7 +3084,7 @@
     </row>
     <row r="13" spans="1:34" ht="16.5">
       <c r="A13" s="26" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B13" s="2">
         <v>5.26185770750988</v>
@@ -3383,123 +3343,55 @@
     </row>
     <row r="19" spans="1:16" ht="16.5">
       <c r="A19" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G19" t="s">
-        <v>50</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="G19"/>
       <c r="H19"/>
-      <c r="I19" t="s">
-        <v>10</v>
-      </c>
+      <c r="I19"/>
       <c r="J19"/>
-      <c r="K19" t="s">
-        <v>51</v>
-      </c>
+      <c r="K19"/>
       <c r="L19"/>
-      <c r="M19" t="s">
-        <v>12</v>
-      </c>
+      <c r="M19"/>
       <c r="N19"/>
       <c r="O19"/>
       <c r="P19"/>
     </row>
     <row r="20" spans="1:16" ht="16.5">
       <c r="A20" s="8"/>
-      <c r="G20">
-        <v>8</v>
-      </c>
-      <c r="H20" s="49">
-        <f>K3/(K3+K4+K5)</f>
-        <v>0.16712364904875632</v>
-      </c>
-      <c r="I20">
-        <v>8</v>
-      </c>
-      <c r="J20" s="49">
-        <f>K6/(K6+K7)</f>
-        <v>3.1192030230161455E-2</v>
-      </c>
-      <c r="K20">
-        <v>8</v>
-      </c>
-      <c r="L20" s="49">
-        <f>K8/(K8+K9+K10)</f>
-        <v>6.1844831318222581E-3</v>
-      </c>
-      <c r="M20">
-        <v>8</v>
-      </c>
-      <c r="N20" s="49">
-        <f>K11/(K11+K12)</f>
-        <v>5.3357626236335241E-2</v>
-      </c>
+      <c r="G20"/>
+      <c r="H20" s="49"/>
+      <c r="I20"/>
+      <c r="J20" s="49"/>
+      <c r="K20"/>
+      <c r="L20" s="49"/>
+      <c r="M20"/>
+      <c r="N20" s="49"/>
       <c r="O20"/>
       <c r="P20"/>
     </row>
     <row r="21" spans="1:16" ht="16.5">
       <c r="A21" s="8"/>
-      <c r="G21">
-        <v>9</v>
-      </c>
-      <c r="H21" s="49">
-        <f>V3/(V3+V4+V5)</f>
-        <v>0.19643916913946591</v>
-      </c>
-      <c r="I21">
-        <v>9</v>
-      </c>
-      <c r="J21" s="49">
-        <f>V6/(V6+V7)</f>
-        <v>5.9028932490854669E-2</v>
-      </c>
-      <c r="K21">
-        <v>9</v>
-      </c>
-      <c r="L21" s="49">
-        <f>V8/(V8+V9+V10)</f>
-        <v>8.2162838921710557E-2</v>
-      </c>
-      <c r="M21">
-        <v>9</v>
-      </c>
-      <c r="N21" s="49">
-        <f>V11/(V11+V12)</f>
-        <v>6.0849471830985963E-2</v>
-      </c>
+      <c r="G21"/>
+      <c r="H21" s="49"/>
+      <c r="I21"/>
+      <c r="J21" s="49"/>
+      <c r="K21"/>
+      <c r="L21" s="49"/>
+      <c r="M21"/>
+      <c r="N21" s="49"/>
       <c r="O21"/>
       <c r="P21"/>
     </row>
     <row r="22" spans="1:16" ht="14.25">
       <c r="E22" s="25"/>
-      <c r="G22">
-        <v>10</v>
-      </c>
-      <c r="H22" s="49">
-        <f>AG3/(AG3+AG4+AG5)</f>
-        <v>0.21338403041825096</v>
-      </c>
-      <c r="I22">
-        <v>10</v>
-      </c>
-      <c r="J22" s="49">
-        <f>AG6/(AG6+AG7)</f>
-        <v>4.2564703760483366E-2</v>
-      </c>
-      <c r="K22">
-        <v>10</v>
-      </c>
-      <c r="L22" s="49">
-        <f>AG8/(AG8+AG9+AG10)</f>
-        <v>0.19721329046087888</v>
-      </c>
-      <c r="M22">
-        <v>10</v>
-      </c>
-      <c r="N22" s="49">
-        <f>AG11/(AG11+AG12)</f>
-        <v>4.6597369603271731E-2</v>
-      </c>
+      <c r="G22"/>
+      <c r="H22" s="49"/>
+      <c r="I22"/>
+      <c r="J22" s="49"/>
+      <c r="K22"/>
+      <c r="L22" s="49"/>
+      <c r="M22"/>
+      <c r="N22" s="49"/>
       <c r="O22"/>
       <c r="P22"/>
     </row>
@@ -3531,1491 +3423,1491 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.5">
       <c r="A1" s="9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5">
       <c r="A2" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C2" s="10"/>
     </row>
     <row r="3" spans="1:3" ht="16.5">
       <c r="A3" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C3" s="10"/>
     </row>
     <row r="4" spans="1:3" ht="16.5">
       <c r="A4" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C4" s="10"/>
     </row>
     <row r="5" spans="1:3" ht="16.5">
       <c r="A5" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C5" s="10"/>
     </row>
     <row r="6" spans="1:3" ht="16.5">
       <c r="A6" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="16.5">
       <c r="A7" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>61</v>
-      </c>
       <c r="C7" s="10" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="16.5">
       <c r="A8" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" spans="1:3" ht="16.5">
       <c r="A9" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C9" s="10"/>
     </row>
     <row r="10" spans="1:3" ht="16.5">
       <c r="A10" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C10" s="10"/>
     </row>
     <row r="11" spans="1:3" ht="16.5">
       <c r="A11" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C11" s="10"/>
     </row>
     <row r="12" spans="1:3" ht="16.5">
       <c r="A12" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C12" s="10"/>
     </row>
     <row r="13" spans="1:3" ht="16.5">
       <c r="A13" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C13" s="10"/>
     </row>
     <row r="14" spans="1:3" ht="16.5">
       <c r="A14" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C14" s="10"/>
     </row>
     <row r="15" spans="1:3" ht="16.5">
       <c r="A15" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C15" s="10"/>
     </row>
     <row r="16" spans="1:3" ht="16.5">
       <c r="A16" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C16" s="10"/>
     </row>
     <row r="17" spans="1:3" ht="16.5">
       <c r="A17" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C17" s="10"/>
     </row>
     <row r="18" spans="1:3" ht="16.5">
       <c r="A18" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C18" s="10"/>
     </row>
     <row r="19" spans="1:3" ht="16.5">
       <c r="A19" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C19" s="11"/>
     </row>
     <row r="20" spans="1:3" ht="16.5">
       <c r="A20" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C20" s="11"/>
     </row>
     <row r="21" spans="1:3" ht="16.5">
       <c r="A21" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C21" s="11"/>
     </row>
     <row r="22" spans="1:3" ht="16.5">
       <c r="A22" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C22" s="11"/>
     </row>
     <row r="23" spans="1:3" ht="16.5">
       <c r="A23" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C23" s="11"/>
     </row>
     <row r="24" spans="1:3" ht="16.5">
       <c r="A24" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>74</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>80</v>
       </c>
       <c r="C24" s="11"/>
     </row>
     <row r="25" spans="1:3" ht="16.5">
       <c r="A25" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C25" s="11"/>
     </row>
     <row r="26" spans="1:3" ht="16.5">
       <c r="A26" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C26" s="11"/>
     </row>
     <row r="27" spans="1:3" ht="16.5">
       <c r="A27" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C27" s="11"/>
     </row>
     <row r="28" spans="1:3" ht="16.5">
       <c r="A28" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C28" s="11"/>
     </row>
     <row r="29" spans="1:3" ht="16.5">
       <c r="A29" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C29" s="11"/>
     </row>
     <row r="30" spans="1:3" ht="16.5">
       <c r="A30" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C30" s="11"/>
     </row>
     <row r="31" spans="1:3" ht="16.5">
       <c r="A31" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C31" s="11"/>
     </row>
     <row r="32" spans="1:3" ht="16.5">
       <c r="A32" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C32" s="11"/>
     </row>
     <row r="33" spans="1:3" ht="16.5">
       <c r="A33" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C33" s="11"/>
     </row>
     <row r="34" spans="1:3" ht="16.5">
       <c r="A34" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C34" s="11"/>
     </row>
     <row r="35" spans="1:3" ht="16.5">
       <c r="A35" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C35" s="11"/>
     </row>
     <row r="36" spans="1:3" ht="16.5">
       <c r="A36" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C36" s="11"/>
     </row>
     <row r="37" spans="1:3" ht="16.5">
       <c r="A37" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C37" s="11"/>
     </row>
     <row r="38" spans="1:3" ht="16.5">
       <c r="A38" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C38" s="11"/>
     </row>
     <row r="39" spans="1:3" ht="16.5">
       <c r="A39" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C39" s="11"/>
     </row>
     <row r="40" spans="1:3" ht="16.5">
       <c r="A40" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C40" s="11"/>
     </row>
     <row r="41" spans="1:3" ht="16.5">
       <c r="A41" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C41" s="10"/>
     </row>
     <row r="42" spans="1:3" ht="16.5">
       <c r="A42" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C42" s="10"/>
     </row>
     <row r="43" spans="1:3" ht="16.5">
       <c r="A43" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C43" s="10"/>
     </row>
     <row r="44" spans="1:3" ht="16.5">
       <c r="A44" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C44" s="10"/>
     </row>
     <row r="45" spans="1:3" ht="16.5">
       <c r="A45" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C45" s="10"/>
     </row>
     <row r="46" spans="1:3" ht="16.5">
       <c r="A46" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>103</v>
       </c>
       <c r="C46" s="10"/>
     </row>
     <row r="47" spans="1:3" ht="16.5">
       <c r="A47" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C47" s="10"/>
     </row>
     <row r="48" spans="1:3" ht="16.5">
       <c r="A48" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C48" s="10"/>
     </row>
     <row r="49" spans="1:3" ht="16.5">
       <c r="A49" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C49" s="10"/>
     </row>
     <row r="50" spans="1:3" ht="16.5">
       <c r="A50" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C50" s="10"/>
     </row>
     <row r="51" spans="1:3" ht="16.5">
       <c r="A51" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C51" s="10"/>
     </row>
     <row r="52" spans="1:3" ht="16.5">
       <c r="A52" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C52" s="10"/>
     </row>
     <row r="53" spans="1:3" ht="16.5">
       <c r="A53" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C53" s="10"/>
     </row>
     <row r="54" spans="1:3" ht="16.5">
       <c r="A54" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C54" s="10"/>
     </row>
     <row r="55" spans="1:3" ht="16.5">
       <c r="A55" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C55" s="10"/>
     </row>
     <row r="56" spans="1:3" ht="16.5">
       <c r="A56" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C56" s="10"/>
     </row>
     <row r="57" spans="1:3" ht="16.5">
       <c r="A57" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C57" s="10"/>
     </row>
     <row r="58" spans="1:3" ht="16.5">
       <c r="A58" s="11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C58" s="11"/>
     </row>
     <row r="59" spans="1:3" ht="16.5">
       <c r="A59" s="11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C59" s="11"/>
     </row>
     <row r="60" spans="1:3" ht="16.5">
       <c r="A60" s="11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C60" s="11"/>
     </row>
     <row r="61" spans="1:3" ht="16.5">
       <c r="A61" s="11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C61" s="11"/>
     </row>
     <row r="62" spans="1:3" ht="16.5">
       <c r="A62" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C62" s="11" t="s">
         <v>115</v>
-      </c>
-      <c r="B62" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="16.5">
       <c r="A63" s="11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C63" s="11"/>
     </row>
     <row r="64" spans="1:3" ht="16.5">
       <c r="A64" s="11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C64" s="11"/>
     </row>
     <row r="65" spans="1:3" ht="16.5">
       <c r="A65" s="11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C65" s="11"/>
     </row>
     <row r="66" spans="1:3" ht="16.5">
       <c r="A66" s="11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C66" s="11"/>
     </row>
     <row r="67" spans="1:3" ht="16.5">
       <c r="A67" s="11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C67" s="11"/>
     </row>
     <row r="68" spans="1:3" ht="16.5">
       <c r="A68" s="11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C68" s="11"/>
     </row>
     <row r="69" spans="1:3" ht="16.5">
       <c r="A69" s="11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C69" s="11"/>
     </row>
     <row r="70" spans="1:3" ht="16.5">
       <c r="A70" s="11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C70" s="11"/>
     </row>
     <row r="71" spans="1:3" ht="16.5">
       <c r="A71" s="11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C71" s="11"/>
     </row>
     <row r="72" spans="1:3" ht="16.5">
       <c r="A72" s="11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C72" s="11"/>
     </row>
     <row r="73" spans="1:3" ht="16.5">
       <c r="A73" s="11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C73" s="11"/>
     </row>
     <row r="74" spans="1:3" ht="16.5">
       <c r="A74" s="10" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C74" s="10"/>
     </row>
     <row r="75" spans="1:3" ht="16.5">
       <c r="A75" s="10" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C75" s="10"/>
     </row>
     <row r="76" spans="1:3" ht="16.5">
       <c r="A76" s="10" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C76" s="10"/>
     </row>
     <row r="77" spans="1:3" ht="16.5">
       <c r="A77" s="10" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C77" s="10"/>
     </row>
     <row r="78" spans="1:3" ht="16.5">
       <c r="A78" s="10" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C78" s="10"/>
     </row>
     <row r="79" spans="1:3" ht="16.5">
       <c r="A79" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B79" s="10" t="s">
         <v>133</v>
-      </c>
-      <c r="B79" s="10" t="s">
-        <v>139</v>
       </c>
       <c r="C79" s="10"/>
     </row>
     <row r="80" spans="1:3" ht="16.5">
       <c r="A80" s="10" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C80" s="10"/>
     </row>
     <row r="81" spans="1:3" ht="16.5">
       <c r="A81" s="10" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C81" s="10"/>
     </row>
     <row r="82" spans="1:3" ht="16.5">
       <c r="A82" s="10" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C82" s="10"/>
     </row>
     <row r="83" spans="1:3" ht="16.5">
       <c r="A83" s="10" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C83" s="10"/>
     </row>
     <row r="84" spans="1:3" ht="16.5">
       <c r="A84" s="10" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C84" s="10"/>
     </row>
     <row r="85" spans="1:3" ht="16.5">
       <c r="A85" s="10" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C85" s="10"/>
     </row>
     <row r="86" spans="1:3" ht="16.5">
       <c r="A86" s="10" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C86" s="10"/>
     </row>
     <row r="87" spans="1:3" ht="16.5">
       <c r="A87" s="10" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C87" s="10"/>
     </row>
     <row r="88" spans="1:3" ht="16.5">
       <c r="A88" s="10" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C88" s="10"/>
     </row>
     <row r="89" spans="1:3" ht="16.5">
       <c r="A89" s="10" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C89" s="10"/>
     </row>
     <row r="90" spans="1:3" ht="16.5">
       <c r="A90" s="10" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C90" s="10"/>
     </row>
     <row r="91" spans="1:3" ht="16.5">
       <c r="A91" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B91" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="B91" s="10" t="s">
-        <v>152</v>
       </c>
       <c r="C91" s="10"/>
     </row>
     <row r="92" spans="1:3" ht="16.5">
       <c r="A92" s="10" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C92" s="10"/>
     </row>
     <row r="93" spans="1:3" ht="16.5">
       <c r="A93" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C93" s="11"/>
     </row>
     <row r="94" spans="1:3" ht="16.5">
       <c r="A94" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C94" s="11"/>
     </row>
     <row r="95" spans="1:3" ht="16.5">
       <c r="A95" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C95" s="11"/>
     </row>
     <row r="96" spans="1:3" ht="16.5">
       <c r="A96" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C96" s="11"/>
     </row>
     <row r="97" spans="1:3" ht="16.5">
       <c r="A97" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="16.5">
       <c r="A98" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B98" s="11" t="s">
         <v>154</v>
-      </c>
-      <c r="B98" s="11" t="s">
-        <v>160</v>
       </c>
       <c r="C98" s="11"/>
     </row>
     <row r="99" spans="1:3" ht="16.5">
       <c r="A99" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C99" s="11"/>
     </row>
     <row r="100" spans="1:3" ht="16.5">
       <c r="A100" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C100" s="11"/>
     </row>
     <row r="101" spans="1:3" ht="16.5">
       <c r="A101" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C101" s="11"/>
     </row>
     <row r="102" spans="1:3" ht="16.5">
       <c r="A102" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C102" s="11"/>
     </row>
     <row r="103" spans="1:3" ht="16.5">
       <c r="A103" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C103" s="11"/>
     </row>
     <row r="104" spans="1:3" ht="16.5">
       <c r="A104" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C104" s="11"/>
     </row>
     <row r="105" spans="1:3" ht="16.5">
       <c r="A105" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C105" s="11"/>
     </row>
     <row r="106" spans="1:3" ht="16.5">
       <c r="A106" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C106" s="11"/>
     </row>
     <row r="107" spans="1:3" ht="16.5">
       <c r="A107" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C107" s="11"/>
     </row>
     <row r="108" spans="1:3" ht="16.5">
       <c r="A108" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C108" s="11"/>
     </row>
     <row r="109" spans="1:3" ht="16.5">
       <c r="A109" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C109" s="11"/>
     </row>
     <row r="110" spans="1:3" ht="16.5">
       <c r="A110" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C110" s="11"/>
     </row>
     <row r="111" spans="1:3" ht="16.5">
       <c r="A111" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C111" s="11"/>
     </row>
     <row r="112" spans="1:3" ht="16.5">
       <c r="A112" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C112" s="11"/>
     </row>
     <row r="113" spans="1:3" ht="16.5">
       <c r="A113" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="16.5">
       <c r="A114" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C114" s="11"/>
     </row>
     <row r="115" spans="1:3" ht="16.5">
       <c r="A115" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C115" s="11"/>
     </row>
     <row r="116" spans="1:3" ht="16.5">
       <c r="A116" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C116" s="11"/>
     </row>
     <row r="117" spans="1:3" ht="16.5">
       <c r="A117" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C117" s="11"/>
     </row>
     <row r="118" spans="1:3" ht="16.5">
       <c r="A118" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C118" s="11"/>
     </row>
     <row r="119" spans="1:3" ht="16.5">
       <c r="A119" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C119" s="11"/>
     </row>
     <row r="120" spans="1:3" ht="16.5">
       <c r="A120" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C120" s="11"/>
     </row>
     <row r="121" spans="1:3" ht="16.5">
       <c r="A121" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C121" s="11"/>
     </row>
     <row r="122" spans="1:3" ht="16.5">
       <c r="A122" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C122" s="11"/>
     </row>
     <row r="123" spans="1:3" ht="16.5">
       <c r="A123" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C123" s="11"/>
     </row>
     <row r="124" spans="1:3" ht="16.5">
       <c r="A124" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C124" s="11"/>
     </row>
     <row r="125" spans="1:3" ht="16.5">
       <c r="A125" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C125" s="11"/>
     </row>
     <row r="126" spans="1:3" ht="16.5">
       <c r="A126" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C126" s="11"/>
     </row>
     <row r="127" spans="1:3" ht="16.5">
       <c r="A127" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C127" s="11"/>
     </row>
     <row r="128" spans="1:3" ht="16.5">
       <c r="A128" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C128" s="11"/>
     </row>
     <row r="129" spans="1:3" ht="16.5">
       <c r="A129" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C129" s="11"/>
     </row>
     <row r="130" spans="1:3" ht="16.5">
       <c r="A130" s="12" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C130" s="11"/>
     </row>
     <row r="131" spans="1:3" ht="16.5">
       <c r="A131" s="10" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C131" s="10"/>
     </row>
     <row r="132" spans="1:3" ht="16.5">
       <c r="A132" s="10" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C132" s="10"/>
     </row>
     <row r="133" spans="1:3" ht="16.5">
       <c r="A133" s="10" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="16.5">
       <c r="A134" s="10" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C134" s="10"/>
     </row>
     <row r="135" spans="1:3" ht="16.5">
       <c r="A135" s="10" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C135" s="10"/>
     </row>
     <row r="136" spans="1:3" ht="16.5">
       <c r="A136" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="B136" s="10" t="s">
         <v>193</v>
-      </c>
-      <c r="B136" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="C136" s="10"/>
     </row>
     <row r="137" spans="1:3" ht="16.5">
       <c r="A137" s="10" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C137" s="10"/>
     </row>
     <row r="138" spans="1:3" ht="16.5">
       <c r="A138" s="10" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C138" s="10"/>
     </row>
     <row r="139" spans="1:3" ht="16.5">
       <c r="A139" s="10" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C139" s="10"/>
     </row>
     <row r="140" spans="1:3" ht="16.5">
       <c r="A140" s="10" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="16.5">
       <c r="A141" s="10" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C141" s="10"/>
     </row>
     <row r="142" spans="1:3" ht="16.5">
       <c r="A142" s="10" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C142" s="10"/>
     </row>
     <row r="143" spans="1:3" ht="16.5">
       <c r="A143" s="10" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C143" s="10"/>
     </row>
     <row r="144" spans="1:3" ht="16.5">
       <c r="A144" s="13" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C144" s="13"/>
     </row>
     <row r="145" spans="1:3" ht="16.5">
       <c r="A145" s="14" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B145" s="14" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C145" s="14"/>
     </row>
     <row r="146" spans="1:3" ht="16.5">
       <c r="A146" s="14" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B146" s="14" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C146" s="14"/>
     </row>
     <row r="147" spans="1:3" ht="16.5">
       <c r="A147" s="14" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B147" s="14" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C147" s="14"/>
     </row>
     <row r="148" spans="1:3" ht="16.5">
       <c r="A148" s="14" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B148" s="14" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C148" s="14"/>
     </row>
     <row r="149" spans="1:3" ht="16.5">
       <c r="A149" s="14" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B149" s="14" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C149" s="14"/>
     </row>
     <row r="150" spans="1:3" ht="16.5">
       <c r="A150" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B150" s="14" t="s">
         <v>209</v>
-      </c>
-      <c r="B150" s="14" t="s">
-        <v>215</v>
       </c>
       <c r="C150" s="14"/>
     </row>
     <row r="151" spans="1:3" ht="16.5">
       <c r="A151" s="14" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B151" s="14" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C151" s="14"/>
     </row>
     <row r="152" spans="1:3" ht="16.5">
       <c r="A152" s="14" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B152" s="14" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C152" s="14"/>
     </row>
     <row r="153" spans="1:3" ht="16.5">
       <c r="A153" s="14" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B153" s="14" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C153" s="14"/>
     </row>
     <row r="154" spans="1:3" ht="16.5">
       <c r="A154" s="14" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B154" s="14" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C154" s="14"/>
     </row>
     <row r="155" spans="1:3" ht="16.5">
       <c r="A155" s="14" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B155" s="14" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C155" s="14"/>
     </row>
     <row r="156" spans="1:3" ht="16.5">
       <c r="A156" s="14" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B156" s="14" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C156" s="14"/>
     </row>
     <row r="157" spans="1:3" ht="16.5">
       <c r="A157" s="14" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B157" s="14" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C157" s="14"/>
     </row>
     <row r="158" spans="1:3" ht="16.5">
       <c r="A158" s="14" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B158" s="14" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C158" s="14"/>
     </row>
     <row r="159" spans="1:3" ht="16.5">
       <c r="A159" s="14" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B159" s="14" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C159" s="14"/>
     </row>
     <row r="160" spans="1:3" ht="16.5">
       <c r="A160" s="15" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B160" s="10" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C160" s="10"/>
     </row>
     <row r="161" spans="1:3" ht="16.5">
       <c r="A161" s="15" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B161" s="10" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C161" s="10"/>
     </row>
     <row r="162" spans="1:3" ht="16.5">
       <c r="A162" s="15" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C162" s="10"/>
     </row>
     <row r="163" spans="1:3" ht="16.5">
       <c r="A163" s="15" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B163" s="10" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C163" s="10"/>
     </row>
     <row r="164" spans="1:3" ht="16.5">
       <c r="A164" s="15" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C164" s="10"/>
     </row>
@@ -5027,6 +4919,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4d11286c-14a7-4966-98ca-64bedb46202e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="1a5b9160-f0ce-4dc9-8d66-d04030c38416" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010050BF04CEA1302844B8519D2D294A3BE8" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="011017bed192b05e47a1ad73019a487a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4d11286c-14a7-4966-98ca-64bedb46202e" xmlns:ns3="1a5b9160-f0ce-4dc9-8d66-d04030c38416" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="96af616972afdc0011c5994c754f78e1" ns2:_="" ns3:_="">
     <xsd:import namespace="4d11286c-14a7-4966-98ca-64bedb46202e"/>
@@ -5255,28 +5167,12 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4d11286c-14a7-4966-98ca-64bedb46202e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="1a5b9160-f0ce-4dc9-8d66-d04030c38416" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4099A34-6BB8-405F-8BE4-C581A9797C45}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EE6AF6F-465F-46CC-8A07-F7E064952E10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5291,9 +5187,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EE6AF6F-465F-46CC-8A07-F7E064952E10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4099A34-6BB8-405F-8BE4-C581A9797C45}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4d11286c-14a7-4966-98ca-64bedb46202e"/>
+    <ds:schemaRef ds:uri="1a5b9160-f0ce-4dc9-8d66-d04030c38416"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>